--- a/jogos_2025-03-05.xlsx
+++ b/jogos_2025-03-05.xlsx
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.89</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>3.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>3.42</v>
+        <v>2.66</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.08</v>
+        <v>3.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['36', '90+1']</t>
-        </is>
-      </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45721.41666666666</v>
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KF Gostivari</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['36', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.17</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45721.41666666666</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Besa Dobërdoll</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '29', '37', '50', '57']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>2.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45721.41666666666</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>KF Gostivari</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
         <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1209,10 +1209,10 @@
         <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
@@ -1224,44 +1224,44 @@
         <v>2.81</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.82</v>
+        <v>3.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>2.16</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['52', '63', '69']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45721.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
         <v>1.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['56', '80']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45721.41666666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Besa Dobërdoll</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,80 +1572,80 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
         <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['52', '63', '69']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['4', '29', '37', '50', '57']</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.4</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
         <v>1.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '80']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45721.41666666666</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['29', '45+6', '77', '90+2']</t>
+          <t>['70', '90+7']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45721.4375</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.41</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['29', '55', '61', '68', '86', '90+1']</t>
+          <t>['29', '45+6', '77', '90+2']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45721.4375</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['70', '90+7']</t>
+          <t>['29', '55', '61', '68', '86', '90+1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45721.4375</v>
@@ -2320,91 +2320,91 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.33</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X15" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['39', '65']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45721.5</v>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.28</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['39', '65']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45721.5</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2862,55 +2862,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y19" t="n">
         <v>2.15</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>1.57</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AA19" t="n">
-        <v>6.35</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
         <v>2.35</v>
@@ -2920,25 +2920,25 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['57', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>2.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45721.60416666666</v>
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>3.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AA21" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['9', '90+6']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI22" t="n">
         <v>3.6</v>
       </c>
-      <c r="N22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Cape Town City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.1</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '90+3']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.23</v>
       </c>
-      <c r="X25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['9', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45721.60416666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Sareeh</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S27" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.7</v>
+        <v>3.09</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['40', '45+2']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45721.66666666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Al Sareeh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.62</v>
       </c>
-      <c r="S28" t="n">
+      <c r="AD28" t="n">
         <v>2.2</v>
       </c>
-      <c r="T28" t="n">
-        <v>4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['40', '45+2']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['45+5']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45721.66666666666</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="P29" t="n">
         <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['39', '71']</t>
+          <t>['46', '90+7']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45721.66666666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.5</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>7.5</v>
+        <v>2.66</v>
       </c>
       <c r="N30" t="n">
-        <v>1.18</v>
+        <v>3.93</v>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.63</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.57</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.5</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="X30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA30" t="n">
         <v>5</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['69', '90+8']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.14</v>
+        <v>2.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45721.66666666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,16 +4384,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.27</v>
+        <v>9.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.66</v>
+        <v>7.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.93</v>
+        <v>1.18</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="R31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.57</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.25</v>
       </c>
-      <c r="T31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['69', '90+8']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>1.14</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45721.66666666666</v>
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="M32" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="P32" t="n">
         <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['39', '71']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.4</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['46', '90+7']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45721.66666666666</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.66</v>
+        <v>2.44</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N35" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U35" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4989,20 +4989,20 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45721.70833333334</v>
@@ -5029,23 +5029,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>1</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.44</v>
+        <v>1.84</v>
       </c>
       <c r="M36" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['9', '54', '75']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.63</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['87']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45721.70833333334</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.84</v>
+        <v>3.66</v>
       </c>
       <c r="M37" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.38</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['9', '54', '75']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45721.70833333334</v>
@@ -5287,23 +5287,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5346,16 +5346,16 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['45+3', '72', '79']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '85']</t>
         </is>
       </c>
       <c r="AG38" t="n">
@@ -5386,10 +5386,10 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45721.72916666666</v>
@@ -5416,76 +5416,76 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA39" t="n">
         <v>0</v>
       </c>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['14', '47', '90+2']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['3', '11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
@@ -5515,10 +5515,10 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45721.72916666666</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5563,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,49 +5571,49 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.85</v>
       </c>
-      <c r="O40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2</v>
-      </c>
       <c r="Z40" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['45+3', '72', '79']</t>
+          <t>['14', '47', '90+2']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['76', '85']</t>
+          <t>['3', '11']</t>
         </is>
       </c>
       <c r="AG40" t="n">
@@ -5644,10 +5644,10 @@
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45721.72916666666</v>
